--- a/GameData/DataTables/Board/BuffTable.xlsx
+++ b/GameData/DataTables/Board/BuffTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>StackRule</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Stackable</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MaxStacks</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TargetPartKind</t>
         </is>
       </c>
     </row>
@@ -477,10 +507,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -494,23 +554,853 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>局内 Buff 的骨架定义</t>
+          <t>局内 Buff 的完整静态定义</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>稳定键（BF-001~BF-020）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Buff 显示名称</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>叠加规则（占位，取值域待 P0-011 冻结）</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>持续轮数，0 表示本关常驻</t>
-        </is>
+          <t>最早进入内容池的玩家阶段</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>玩家可见效果描述</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是否允许叠加</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>最大叠加层数</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BuffEffectKind 数值</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>每层效果数值</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>作用零件 PartType 数值，0 表示通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BF-001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>精密计量</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>计量棘轮每次触发分+2（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BF-002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>全盘校准</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>场上所有零件每次触发分+1（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BF-003</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>重击记录</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>惯性撞锤每实际反推1格，效果分+4（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BF-004</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>爆点记录</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>爆破线圈每波及一个有效对象，效果分+3（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BF-005</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>转向记录</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>换向齿轮每次成功换向推进，效果分+4（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BF-006</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>飞轮测量</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>蓄能飞轮释放时，每个射线命中对象的效果分+3（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BF-007</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>清晰显影</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>照明棱镜每揭露1层伪装，效果分+4（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BF-008</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>排水记录</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>排水叶轮每实际排掉1单位水，效果分+4（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BF-009</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>牵引记录</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>磁吸牵引器每实际牵引1格，效果分+3（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BF-010</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>补能记录</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>接力电池每实际转移1点能量，效果分+4（最多叠加5次）。</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BF-011</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>增产棘轮</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>计量棘轮每次成功产能，额外产生1点公共维修能量（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BF-012</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>扩容补能</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>有自身能量槽的零件容量+1，场上已有零件立即补能1；后续生成按条目获得对应加成（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BF-013</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>充足备件</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>之后通过补给生成的有能量槽零件，初始能量与容量各+1（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BF-014</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>回收余振</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>每拍结束时产生1点公共维修能量（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BF-015</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>轮间保养</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>后续每轮开始时，场上有能量槽的零件各恢复1点能量，不超过容量（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BF-016</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>长程撞锤</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>惯性撞锤反推距离+1格（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BF-017</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>加长弹簧</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>弹射簧弹射距离+1格（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BF-018</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>远距磁吸</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>磁吸牵引器搜索距离+1格，牵引距离保持原值（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BF-019</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>大口径叶轮</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>排水叶轮单次排水上限+1（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BF-020</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>轮间调臂</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>后续每轮开始时，机械臂次数+1（最多叠加3次）。</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
